--- a/Deliverables/BOM/Electrode-Board/eSpark_BOM_Electrode_Board.xlsx
+++ b/Deliverables/BOM/Electrode-Board/eSpark_BOM_Electrode_Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ManarHarake-sEMGDevice\Deliverables\BOM\Electrode-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A15EA897-496E-4B60-A0A2-124B7B811F21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC459D7C-E4B6-4D53-8BE8-F033A6C26C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="113">
   <si>
     <t>Component list</t>
   </si>
@@ -366,6 +366,9 @@
   </si>
   <si>
     <t>C110221</t>
+  </si>
+  <si>
+    <t>Need Fresh Quotation From Custom Supplier</t>
   </si>
 </sst>
 </file>
@@ -377,7 +380,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -551,8 +554,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -583,6 +594,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="27">
     <border>
@@ -903,7 +920,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1068,18 +1085,69 @@
     <xf numFmtId="165" fontId="23" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="2" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1090,57 +1158,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="2" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1151,22 +1168,49 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1541,15 +1585,15 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="62"/>
-      <c r="R1" s="63"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="81"/>
+      <c r="Q1" s="81"/>
+      <c r="R1" s="82"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1596,8 +1640,8 @@
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
-      <c r="Q3" s="91"/>
-      <c r="R3" s="64"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="90"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1620,8 +1664,8 @@
       <c r="N4" s="6"/>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
-      <c r="Q4" s="92"/>
-      <c r="R4" s="65"/>
+      <c r="Q4" s="91"/>
+      <c r="R4" s="92"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1644,8 +1688,8 @@
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
-      <c r="Q5" s="92"/>
-      <c r="R5" s="65"/>
+      <c r="Q5" s="91"/>
+      <c r="R5" s="92"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1664,8 +1708,8 @@
       <c r="N6" s="6"/>
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
-      <c r="Q6" s="92"/>
-      <c r="R6" s="65"/>
+      <c r="Q6" s="91"/>
+      <c r="R6" s="92"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1684,8 +1728,8 @@
       <c r="N7" s="8"/>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
-      <c r="Q7" s="92"/>
-      <c r="R7" s="65"/>
+      <c r="Q7" s="91"/>
+      <c r="R7" s="92"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1724,7 +1768,7 @@
       <c r="F9" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="G9" s="77" t="s">
+      <c r="G9" s="69" t="s">
         <v>77</v>
       </c>
       <c r="H9" s="30" t="s">
@@ -1779,7 +1823,7 @@
       <c r="F10" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="G10" s="80" t="s">
+      <c r="G10" s="72" t="s">
         <v>90</v>
       </c>
       <c r="H10" s="43" t="s">
@@ -1807,7 +1851,7 @@
       <c r="O10" s="61">
         <v>1.3599999999999999E-2</v>
       </c>
-      <c r="P10" s="71">
+      <c r="P10" s="63">
         <f>O10*M10</f>
         <v>0.81599999999999995</v>
       </c>
@@ -1829,10 +1873,10 @@
       <c r="E11" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="79" t="s">
+      <c r="F11" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="G11" s="81" t="s">
+      <c r="G11" s="73" t="s">
         <v>86</v>
       </c>
       <c r="H11" s="47" t="s">
@@ -1907,7 +1951,7 @@
       <c r="M12" s="43">
         <v>100</v>
       </c>
-      <c r="N12" s="74" t="s">
+      <c r="N12" s="66" t="s">
         <v>88</v>
       </c>
       <c r="O12" s="43">
@@ -1938,7 +1982,7 @@
       <c r="F13" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="G13" s="72" t="s">
+      <c r="G13" s="64" t="s">
         <v>90</v>
       </c>
       <c r="H13" s="47" t="s">
@@ -1957,7 +2001,7 @@
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="M13" s="73">
+      <c r="M13" s="65">
         <v>50</v>
       </c>
       <c r="N13" s="54" t="s">
@@ -2013,10 +2057,10 @@
       <c r="M14" s="43">
         <v>100</v>
       </c>
-      <c r="N14" s="74" t="s">
+      <c r="N14" s="66" t="s">
         <v>88</v>
       </c>
-      <c r="O14" s="70">
+      <c r="O14" s="62">
         <v>1.3100000000000001E-2</v>
       </c>
       <c r="P14" s="57">
@@ -2044,7 +2088,7 @@
       <c r="F15" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="72" t="s">
+      <c r="G15" s="64" t="s">
         <v>90</v>
       </c>
       <c r="H15" s="47" t="s">
@@ -2053,7 +2097,7 @@
       <c r="I15" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="J15" s="72" t="s">
+      <c r="J15" s="64" t="s">
         <v>97</v>
       </c>
       <c r="K15" s="48">
@@ -2066,10 +2110,10 @@
       <c r="M15" s="47">
         <v>42</v>
       </c>
-      <c r="N15" s="75" t="s">
+      <c r="N15" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="O15" s="85">
+      <c r="O15" s="77">
         <v>0.1094</v>
       </c>
       <c r="P15" s="56">
@@ -2094,7 +2138,7 @@
       <c r="E16" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="F16" s="76" t="s">
+      <c r="F16" s="68" t="s">
         <v>99</v>
       </c>
       <c r="G16" s="59" t="s">
@@ -2103,7 +2147,7 @@
       <c r="H16" s="59" t="s">
         <v>99</v>
       </c>
-      <c r="I16" s="76" t="s">
+      <c r="I16" s="68" t="s">
         <v>99</v>
       </c>
       <c r="J16" s="59" t="s">
@@ -2122,16 +2166,16 @@
       <c r="N16" s="59" t="s">
         <v>99</v>
       </c>
-      <c r="O16" s="86" t="s">
+      <c r="O16" s="78" t="s">
         <v>100</v>
       </c>
-      <c r="P16" s="82" t="s">
+      <c r="P16" s="74" t="s">
         <v>90</v>
       </c>
-      <c r="Q16" s="83" t="s">
+      <c r="Q16" s="75" t="s">
         <v>90</v>
       </c>
-      <c r="R16" s="84" t="s">
+      <c r="R16" s="76" t="s">
         <v>100</v>
       </c>
     </row>
@@ -2153,7 +2197,7 @@
       <c r="F17" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="G17" s="72" t="s">
+      <c r="G17" s="64" t="s">
         <v>90</v>
       </c>
       <c r="H17" s="47" t="s">
@@ -2175,10 +2219,10 @@
       <c r="M17" s="47">
         <v>100</v>
       </c>
-      <c r="N17" s="75" t="s">
+      <c r="N17" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="O17" s="85">
+      <c r="O17" s="77">
         <v>8.0000000000000004E-4</v>
       </c>
       <c r="P17" s="56">
@@ -2228,10 +2272,10 @@
       <c r="M18" s="43">
         <v>300</v>
       </c>
-      <c r="N18" s="74" t="s">
+      <c r="N18" s="66" t="s">
         <v>88</v>
       </c>
-      <c r="O18" s="70">
+      <c r="O18" s="62">
         <v>5.0000000000000001E-4</v>
       </c>
       <c r="P18" s="57">
@@ -2259,7 +2303,7 @@
       <c r="F19" s="48" t="s">
         <v>103</v>
       </c>
-      <c r="G19" s="72" t="s">
+      <c r="G19" s="64" t="s">
         <v>90</v>
       </c>
       <c r="H19" s="47" t="s">
@@ -2281,10 +2325,10 @@
       <c r="M19" s="47">
         <v>100</v>
       </c>
-      <c r="N19" s="75" t="s">
+      <c r="N19" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="O19" s="85">
+      <c r="O19" s="77">
         <v>6.9999999999999999E-4</v>
       </c>
       <c r="P19" s="56">
@@ -2334,10 +2378,10 @@
       <c r="M20" s="43">
         <v>45</v>
       </c>
-      <c r="N20" s="74" t="s">
+      <c r="N20" s="66" t="s">
         <v>88</v>
       </c>
-      <c r="O20" s="70">
+      <c r="O20" s="62">
         <v>0.18210000000000001</v>
       </c>
       <c r="P20" s="57">
@@ -2365,7 +2409,7 @@
       <c r="F21" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="G21" s="72" t="s">
+      <c r="G21" s="64" t="s">
         <v>90</v>
       </c>
       <c r="H21" s="47" t="s">
@@ -2387,10 +2431,10 @@
       <c r="M21" s="47">
         <v>100</v>
       </c>
-      <c r="N21" s="75" t="s">
+      <c r="N21" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="O21" s="85">
+      <c r="O21" s="77">
         <v>5.9999999999999995E-4</v>
       </c>
       <c r="P21" s="56">
@@ -2406,52 +2450,52 @@
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
-      <c r="C22" s="43" t="s">
+      <c r="C22" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="44" t="s">
+      <c r="D22" s="96" t="s">
         <v>38</v>
       </c>
-      <c r="E22" s="43" t="s">
+      <c r="E22" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="F22" s="44" t="s">
+      <c r="F22" s="96" t="s">
         <v>57</v>
       </c>
-      <c r="G22" s="59" t="s">
+      <c r="G22" s="97" t="s">
         <v>99</v>
       </c>
-      <c r="H22" s="43" t="s">
+      <c r="H22" s="95" t="s">
         <v>66</v>
       </c>
-      <c r="I22" s="83" t="s">
+      <c r="I22" s="98" t="s">
         <v>100</v>
       </c>
-      <c r="J22" s="59" t="s">
+      <c r="J22" s="97" t="s">
         <v>97</v>
       </c>
-      <c r="K22" s="44">
+      <c r="K22" s="96">
         <v>1</v>
       </c>
-      <c r="L22" s="43">
+      <c r="L22" s="95">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="M22" s="43">
+      <c r="M22" s="95">
         <v>42</v>
       </c>
-      <c r="N22" s="74" t="s">
+      <c r="N22" s="99" t="s">
         <v>107</v>
       </c>
-      <c r="O22" s="70">
-        <v>4.55</v>
-      </c>
-      <c r="P22" s="57">
+      <c r="O22" s="100"/>
+      <c r="P22" s="101">
         <f t="shared" si="2"/>
-        <v>191.1</v>
-      </c>
-      <c r="Q22" s="45"/>
-      <c r="R22" s="51"/>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="102" t="s">
+        <v>112</v>
+      </c>
+      <c r="R22" s="103"/>
     </row>
     <row r="23" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
@@ -2471,16 +2515,16 @@
       <c r="F23" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="G23" s="72" t="s">
+      <c r="G23" s="64" t="s">
         <v>90</v>
       </c>
-      <c r="H23" s="78" t="s">
+      <c r="H23" s="70" t="s">
         <v>67</v>
       </c>
       <c r="I23" s="49" t="s">
         <v>108</v>
       </c>
-      <c r="J23" s="72" t="s">
+      <c r="J23" s="64" t="s">
         <v>97</v>
       </c>
       <c r="K23" s="48">
@@ -2493,10 +2537,10 @@
       <c r="M23" s="47">
         <v>42</v>
       </c>
-      <c r="N23" s="75" t="s">
+      <c r="N23" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="O23" s="85">
+      <c r="O23" s="77">
         <v>0.32100000000000001</v>
       </c>
       <c r="P23" s="56">
@@ -2526,12 +2570,12 @@
       </c>
       <c r="N24" s="88"/>
       <c r="O24" s="88"/>
-      <c r="P24" s="89">
+      <c r="P24" s="79">
         <f>SUM(P10:P23)</f>
-        <v>220.64230000000001</v>
-      </c>
-      <c r="Q24" s="66"/>
-      <c r="R24" s="67"/>
+        <v>29.542300000000004</v>
+      </c>
+      <c r="Q24" s="83"/>
+      <c r="R24" s="84"/>
     </row>
     <row r="25" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
@@ -2553,12 +2597,12 @@
       </c>
       <c r="N25" s="88"/>
       <c r="O25" s="88"/>
-      <c r="P25" s="90">
-        <f>P24/5</f>
-        <v>44.128460000000004</v>
-      </c>
-      <c r="Q25" s="68"/>
-      <c r="R25" s="69"/>
+      <c r="P25" s="80">
+        <f>P24/40</f>
+        <v>0.73855750000000009</v>
+      </c>
+      <c r="Q25" s="85"/>
+      <c r="R25" s="86"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/Deliverables/BOM/Electrode-Board/eSpark_BOM_Electrode_Board.xlsx
+++ b/Deliverables/BOM/Electrode-Board/eSpark_BOM_Electrode_Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ManarHarake-sEMGDevice\Deliverables\BOM\Electrode-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC459D7C-E4B6-4D53-8BE8-F033A6C26C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB5A6380-A497-4E6A-9423-06C3601B9572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="112">
   <si>
     <t>Component list</t>
   </si>
@@ -80,9 +80,6 @@
     <t>D1, D2</t>
   </si>
   <si>
-    <t>J1</t>
-  </si>
-  <si>
     <t>P1</t>
   </si>
   <si>
@@ -125,9 +122,6 @@
     <t>100V -55℃~+150℃@(Tj) 400mW Single 1.25V@150mA 4ns 1μA@75V 200mA SOD-323 Switching Diode ROHS</t>
   </si>
   <si>
-    <t>CONN FFC BOTTOM 6POS 0.50MM R/A</t>
-  </si>
-  <si>
     <t>Sensor Connecting Pads</t>
   </si>
   <si>
@@ -164,9 +158,6 @@
     <t>SOD-323</t>
   </si>
   <si>
-    <t>FH19C-6S-0.5SH(10)</t>
-  </si>
-  <si>
     <t>Res0402</t>
   </si>
   <si>
@@ -221,9 +212,6 @@
     <t>Yageo</t>
   </si>
   <si>
-    <t>Hirose</t>
-  </si>
-  <si>
     <t>FH</t>
   </si>
   <si>
@@ -260,9 +248,6 @@
     <t>1K</t>
   </si>
   <si>
-    <t>Quantity</t>
-  </si>
-  <si>
     <t>Alternate Part No</t>
   </si>
   <si>
@@ -326,9 +311,6 @@
     <t>----</t>
   </si>
   <si>
-    <t>C424651</t>
-  </si>
-  <si>
     <t>-------</t>
   </si>
   <si>
@@ -353,9 +335,6 @@
     <t>C105637</t>
   </si>
   <si>
-    <t>Custom Supplier</t>
-  </si>
-  <si>
     <t>C85344</t>
   </si>
   <si>
@@ -369,6 +348,24 @@
   </si>
   <si>
     <t>Need Fresh Quotation From Custom Supplier</t>
+  </si>
+  <si>
+    <t>P9</t>
+  </si>
+  <si>
+    <t>Ribbon wire Connection Pads</t>
+  </si>
+  <si>
+    <t>6 pin Ribbon Pads.</t>
+  </si>
+  <si>
+    <t>100K</t>
+  </si>
+  <si>
+    <t>DO NOT MOUNT</t>
+  </si>
+  <si>
+    <t>Quantity (1 Board)</t>
   </si>
 </sst>
 </file>
@@ -380,7 +377,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -392,6 +389,7 @@
       <sz val="10"/>
       <color indexed="13"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -405,6 +403,7 @@
       <sz val="12"/>
       <color indexed="13"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -557,6 +556,22 @@
     <font>
       <b/>
       <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -601,7 +616,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -913,6 +928,17 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -920,7 +946,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1103,9 +1129,6 @@
     <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1121,25 +1144,85 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="2" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="18" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="4" borderId="16" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="26" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1184,33 +1267,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1248,7 +1304,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>1724025</xdr:colOff>
+      <xdr:colOff>1724026</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>180975</xdr:rowOff>
     </xdr:to>
@@ -1560,17 +1616,19 @@
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
     <col min="3" max="3" width="36" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.42578125" customWidth="1"/>
-    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.42578125" customWidth="1"/>
-    <col min="10" max="10" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="29.42578125" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.85546875" customWidth="1"/>
+    <col min="4" max="4" width="28.140625" customWidth="1"/>
+    <col min="5" max="5" width="21.5703125" customWidth="1"/>
+    <col min="6" max="6" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="29.42578125" customWidth="1"/>
     <col min="18" max="18" width="26.85546875" bestFit="1" customWidth="1"/>
   </cols>
@@ -1585,15 +1643,15 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81"/>
-      <c r="N1" s="81"/>
-      <c r="O1" s="81"/>
-      <c r="P1" s="81"/>
-      <c r="Q1" s="81"/>
-      <c r="R1" s="82"/>
+      <c r="J1" s="100"/>
+      <c r="K1" s="100"/>
+      <c r="L1" s="100"/>
+      <c r="M1" s="100"/>
+      <c r="N1" s="100"/>
+      <c r="O1" s="100"/>
+      <c r="P1" s="100"/>
+      <c r="Q1" s="100"/>
+      <c r="R1" s="101"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1640,8 +1698,8 @@
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
-      <c r="Q3" s="89"/>
-      <c r="R3" s="90"/>
+      <c r="Q3" s="108"/>
+      <c r="R3" s="109"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1664,8 +1722,8 @@
       <c r="N4" s="6"/>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
-      <c r="Q4" s="91"/>
-      <c r="R4" s="92"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="111"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1688,8 +1746,8 @@
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
-      <c r="Q5" s="91"/>
-      <c r="R5" s="92"/>
+      <c r="Q5" s="110"/>
+      <c r="R5" s="111"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1708,8 +1766,8 @@
       <c r="N6" s="6"/>
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
-      <c r="Q6" s="91"/>
-      <c r="R6" s="92"/>
+      <c r="Q6" s="110"/>
+      <c r="R6" s="111"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1728,8 +1786,8 @@
       <c r="N7" s="8"/>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
-      <c r="Q7" s="91"/>
-      <c r="R7" s="92"/>
+      <c r="Q7" s="110"/>
+      <c r="R7" s="111"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1748,8 +1806,8 @@
       <c r="N8" s="8"/>
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
-      <c r="Q8" s="93"/>
-      <c r="R8" s="94"/>
+      <c r="Q8" s="112"/>
+      <c r="R8" s="113"/>
     </row>
     <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1760,49 +1818,49 @@
         <v>10</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" s="69" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="68" t="s">
+        <v>72</v>
+      </c>
+      <c r="H9" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="I9" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="K9" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="N9" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="O9" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="H9" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="I9" s="32" t="s">
+      <c r="P9" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="J9" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="K9" s="31" t="s">
+      <c r="Q9" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="R9" s="32" t="s">
         <v>76</v>
-      </c>
-      <c r="L9" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="M9" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="N9" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="O9" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="P9" s="30" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q9" s="32" t="s">
-        <v>80</v>
-      </c>
-      <c r="R9" s="32" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1815,25 +1873,25 @@
         <v>11</v>
       </c>
       <c r="D10" s="44" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E10" s="43" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F10" s="44" t="s">
-        <v>50</v>
-      </c>
-      <c r="G10" s="72" t="s">
-        <v>90</v>
+        <v>47</v>
+      </c>
+      <c r="G10" s="71" t="s">
+        <v>85</v>
       </c>
       <c r="H10" s="43" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I10" s="58" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="J10" s="43" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="K10" s="44">
         <v>1</v>
@@ -1846,7 +1904,7 @@
         <v>60</v>
       </c>
       <c r="N10" s="60" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="O10" s="61">
         <v>1.3599999999999999E-2</v>
@@ -1855,7 +1913,7 @@
         <f>O10*M10</f>
         <v>0.81599999999999995</v>
       </c>
-      <c r="Q10" s="45"/>
+      <c r="Q10" s="43"/>
       <c r="R10" s="46"/>
     </row>
     <row r="11" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1868,25 +1926,25 @@
         <v>12</v>
       </c>
       <c r="D11" s="48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E11" s="47" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="71" t="s">
-        <v>51</v>
-      </c>
-      <c r="G11" s="73" t="s">
-        <v>86</v>
+        <v>40</v>
+      </c>
+      <c r="F11" s="70" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" s="72" t="s">
+        <v>81</v>
       </c>
       <c r="H11" s="47" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I11" s="52" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J11" s="47" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="K11" s="48">
         <v>1</v>
@@ -1899,47 +1957,47 @@
         <v>50</v>
       </c>
       <c r="N11" s="54" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="O11" s="55">
-        <v>7.3000000000000001E-3</v>
+        <v>7.1999999999999998E-3</v>
       </c>
       <c r="P11" s="56">
         <f>O11*M11</f>
-        <v>0.36499999999999999</v>
-      </c>
-      <c r="Q11" s="49"/>
+        <v>0.36</v>
+      </c>
+      <c r="Q11" s="47"/>
       <c r="R11" s="50"/>
     </row>
     <row r="12" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="38">
-        <f>ROW(B12) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="C12" s="43" t="s">
         <v>13</v>
       </c>
       <c r="D12" s="44" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E12" s="43" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F12" s="44" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G12" s="59" t="s">
+        <v>85</v>
+      </c>
+      <c r="H12" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="I12" s="45" t="s">
         <v>90</v>
       </c>
-      <c r="H12" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="I12" s="45" t="s">
-        <v>95</v>
-      </c>
       <c r="J12" s="43" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="K12" s="44">
         <v>1</v>
@@ -1952,7 +2010,7 @@
         <v>100</v>
       </c>
       <c r="N12" s="66" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="O12" s="43">
         <v>1E-3</v>
@@ -1961,7 +2019,7 @@
         <f t="shared" ref="P12:P23" si="2">O12*M12</f>
         <v>0.1</v>
       </c>
-      <c r="Q12" s="45"/>
+      <c r="Q12" s="43"/>
       <c r="R12" s="51"/>
     </row>
     <row r="13" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1974,25 +2032,25 @@
         <v>14</v>
       </c>
       <c r="D13" s="48" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E13" s="47" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F13" s="48" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G13" s="64" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H13" s="47" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I13" s="52" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="J13" s="47" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="K13" s="48">
         <v>1</v>
@@ -2005,47 +2063,47 @@
         <v>50</v>
       </c>
       <c r="N13" s="54" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="O13" s="55">
-        <v>6.4000000000000003E-3</v>
+        <v>6.7000000000000002E-3</v>
       </c>
       <c r="P13" s="56">
         <f t="shared" si="2"/>
-        <v>0.32</v>
-      </c>
-      <c r="Q13" s="49"/>
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="Q13" s="47"/>
       <c r="R13" s="50"/>
     </row>
-    <row r="14" spans="1:18" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="38">
-        <f>ROW(B14) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C14" s="43" t="s">
         <v>15</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E14" s="43" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F14" s="44" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G14" s="59" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H14" s="43" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="I14" s="45" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="J14" s="59" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="K14" s="44">
         <v>2</v>
@@ -2058,7 +2116,7 @@
         <v>100</v>
       </c>
       <c r="N14" s="66" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="O14" s="62">
         <v>1.3100000000000001E-2</v>
@@ -2067,7 +2125,7 @@
         <f t="shared" si="2"/>
         <v>1.31</v>
       </c>
-      <c r="Q14" s="45"/>
+      <c r="Q14" s="43"/>
       <c r="R14" s="51"/>
     </row>
     <row r="15" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2076,107 +2134,109 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="47" t="s">
+      <c r="C15" s="92" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="47" t="s">
+      <c r="D15" s="93" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="92" t="s">
+        <v>88</v>
+      </c>
+      <c r="F15" s="94" t="s">
         <v>93</v>
       </c>
-      <c r="F15" s="48" t="s">
-        <v>44</v>
-      </c>
-      <c r="G15" s="64" t="s">
-        <v>90</v>
-      </c>
-      <c r="H15" s="47" t="s">
-        <v>63</v>
-      </c>
-      <c r="I15" s="49" t="s">
-        <v>98</v>
-      </c>
-      <c r="J15" s="64" t="s">
-        <v>97</v>
-      </c>
-      <c r="K15" s="48">
+      <c r="G15" s="95" t="s">
+        <v>93</v>
+      </c>
+      <c r="H15" s="95" t="s">
+        <v>93</v>
+      </c>
+      <c r="I15" s="94" t="s">
+        <v>93</v>
+      </c>
+      <c r="J15" s="95" t="s">
+        <v>92</v>
+      </c>
+      <c r="K15" s="93">
         <v>1</v>
       </c>
-      <c r="L15" s="53">
+      <c r="L15" s="92">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="M15" s="47">
-        <v>42</v>
-      </c>
-      <c r="N15" s="67" t="s">
-        <v>88</v>
-      </c>
-      <c r="O15" s="77">
-        <v>0.1094</v>
-      </c>
-      <c r="P15" s="56">
-        <f t="shared" si="2"/>
-        <v>4.5948000000000002</v>
-      </c>
-      <c r="Q15" s="49"/>
-      <c r="R15" s="50"/>
+      <c r="M15" s="95" t="s">
+        <v>94</v>
+      </c>
+      <c r="N15" s="95" t="s">
+        <v>93</v>
+      </c>
+      <c r="O15" s="96" t="s">
+        <v>94</v>
+      </c>
+      <c r="P15" s="97" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q15" s="98" t="s">
+        <v>110</v>
+      </c>
+      <c r="R15" s="99" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="16" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="38">
-        <f>ROW(B16) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="43" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="44" t="s">
-        <v>32</v>
-      </c>
-      <c r="E16" s="43" t="s">
+      <c r="C16" s="84" t="s">
+        <v>106</v>
+      </c>
+      <c r="D16" s="85" t="s">
+        <v>107</v>
+      </c>
+      <c r="E16" s="89" t="s">
+        <v>88</v>
+      </c>
+      <c r="F16" s="84" t="s">
+        <v>108</v>
+      </c>
+      <c r="G16" s="87" t="s">
         <v>93</v>
       </c>
-      <c r="F16" s="68" t="s">
-        <v>99</v>
-      </c>
-      <c r="G16" s="59" t="s">
-        <v>99</v>
-      </c>
-      <c r="H16" s="59" t="s">
-        <v>99</v>
-      </c>
-      <c r="I16" s="68" t="s">
-        <v>99</v>
-      </c>
-      <c r="J16" s="59" t="s">
-        <v>97</v>
-      </c>
-      <c r="K16" s="44">
+      <c r="H16" s="87" t="s">
+        <v>93</v>
+      </c>
+      <c r="I16" s="86" t="s">
+        <v>93</v>
+      </c>
+      <c r="J16" s="87" t="s">
+        <v>92</v>
+      </c>
+      <c r="K16" s="87">
         <v>1</v>
       </c>
-      <c r="L16" s="43">
-        <f t="shared" si="1"/>
+      <c r="L16" s="87">
         <v>40</v>
       </c>
-      <c r="M16" s="59" t="s">
-        <v>100</v>
-      </c>
-      <c r="N16" s="59" t="s">
-        <v>99</v>
-      </c>
-      <c r="O16" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="P16" s="74" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q16" s="75" t="s">
-        <v>90</v>
-      </c>
-      <c r="R16" s="76" t="s">
-        <v>100</v>
+      <c r="M16" s="86" t="s">
+        <v>93</v>
+      </c>
+      <c r="N16" s="87" t="s">
+        <v>92</v>
+      </c>
+      <c r="O16" s="87" t="s">
+        <v>93</v>
+      </c>
+      <c r="P16" s="87" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q16" s="90" t="s">
+        <v>110</v>
+      </c>
+      <c r="R16" s="88" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2186,28 +2246,28 @@
         <v>8</v>
       </c>
       <c r="C17" s="47" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D17" s="48" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E17" s="47" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F17" s="48" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G17" s="64" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H17" s="47" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I17" s="49" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="J17" s="47" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="K17" s="48">
         <v>1</v>
@@ -2220,47 +2280,47 @@
         <v>100</v>
       </c>
       <c r="N17" s="67" t="s">
-        <v>88</v>
-      </c>
-      <c r="O17" s="77">
+        <v>83</v>
+      </c>
+      <c r="O17" s="73">
         <v>8.0000000000000004E-4</v>
       </c>
       <c r="P17" s="56">
         <f t="shared" si="2"/>
         <v>0.08</v>
       </c>
-      <c r="Q17" s="49"/>
+      <c r="Q17" s="47"/>
       <c r="R17" s="50"/>
     </row>
     <row r="18" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="38">
-        <f>ROW(B18) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="C18" s="43" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D18" s="44" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E18" s="43" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F18" s="44" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G18" s="59" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="H18" s="43" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I18" s="45" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="J18" s="43" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K18" s="44">
         <v>5</v>
@@ -2273,7 +2333,7 @@
         <v>300</v>
       </c>
       <c r="N18" s="66" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="O18" s="62">
         <v>5.0000000000000001E-4</v>
@@ -2282,38 +2342,38 @@
         <f t="shared" si="2"/>
         <v>0.15</v>
       </c>
-      <c r="Q18" s="45"/>
+      <c r="Q18" s="43"/>
       <c r="R18" s="51"/>
     </row>
-    <row r="19" spans="1:18" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="38">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="C19" s="47" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D19" s="48" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E19" s="47" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F19" s="48" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="G19" s="64" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H19" s="47" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I19" s="49" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="J19" s="47" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="K19" s="48">
         <v>2</v>
@@ -2326,47 +2386,47 @@
         <v>100</v>
       </c>
       <c r="N19" s="67" t="s">
-        <v>88</v>
-      </c>
-      <c r="O19" s="77">
+        <v>83</v>
+      </c>
+      <c r="O19" s="73">
         <v>6.9999999999999999E-4</v>
       </c>
       <c r="P19" s="56">
         <f t="shared" si="2"/>
         <v>6.9999999999999993E-2</v>
       </c>
-      <c r="Q19" s="49"/>
+      <c r="Q19" s="47"/>
       <c r="R19" s="50"/>
     </row>
     <row r="20" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="38">
-        <f>ROW(B20) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="C20" s="43" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D20" s="44" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E20" s="43" t="s">
+        <v>88</v>
+      </c>
+      <c r="F20" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="G20" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="F20" s="44" t="s">
-        <v>46</v>
-      </c>
-      <c r="G20" s="59" t="s">
+      <c r="H20" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="I20" s="45" t="s">
         <v>99</v>
       </c>
-      <c r="H20" s="43" t="s">
-        <v>65</v>
-      </c>
-      <c r="I20" s="45" t="s">
-        <v>105</v>
-      </c>
       <c r="J20" s="59" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="K20" s="44">
         <v>1</v>
@@ -2379,7 +2439,7 @@
         <v>45</v>
       </c>
       <c r="N20" s="66" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="O20" s="62">
         <v>0.18210000000000001</v>
@@ -2388,7 +2448,7 @@
         <f t="shared" si="2"/>
         <v>8.1944999999999997</v>
       </c>
-      <c r="Q20" s="45"/>
+      <c r="Q20" s="43"/>
       <c r="R20" s="51"/>
     </row>
     <row r="21" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2398,28 +2458,28 @@
         <v>12</v>
       </c>
       <c r="C21" s="47" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D21" s="48" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E21" s="47" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F21" s="48" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G21" s="64" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H21" s="47" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I21" s="49" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="J21" s="47" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="K21" s="48">
         <v>1</v>
@@ -2432,70 +2492,68 @@
         <v>100</v>
       </c>
       <c r="N21" s="67" t="s">
-        <v>88</v>
-      </c>
-      <c r="O21" s="77">
+        <v>83</v>
+      </c>
+      <c r="O21" s="73">
         <v>5.9999999999999995E-4</v>
       </c>
       <c r="P21" s="56">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
-      <c r="Q21" s="49"/>
+      <c r="Q21" s="47"/>
       <c r="R21" s="50"/>
     </row>
-    <row r="22" spans="1:18" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="38">
-        <f>ROW(B22) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="95" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22" s="96" t="s">
-        <v>38</v>
-      </c>
-      <c r="E22" s="95" t="s">
-        <v>47</v>
-      </c>
-      <c r="F22" s="96" t="s">
-        <v>57</v>
-      </c>
-      <c r="G22" s="97" t="s">
-        <v>99</v>
-      </c>
-      <c r="H22" s="95" t="s">
-        <v>66</v>
-      </c>
-      <c r="I22" s="98" t="s">
-        <v>100</v>
-      </c>
-      <c r="J22" s="97" t="s">
-        <v>97</v>
-      </c>
-      <c r="K22" s="96">
+      <c r="C22" s="76" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" s="77" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="76" t="s">
+        <v>44</v>
+      </c>
+      <c r="F22" s="77" t="s">
+        <v>54</v>
+      </c>
+      <c r="G22" s="78" t="s">
+        <v>93</v>
+      </c>
+      <c r="H22" s="76" t="s">
+        <v>62</v>
+      </c>
+      <c r="I22" s="79" t="s">
+        <v>94</v>
+      </c>
+      <c r="J22" s="78" t="s">
+        <v>92</v>
+      </c>
+      <c r="K22" s="77">
         <v>1</v>
       </c>
-      <c r="L22" s="95">
+      <c r="L22" s="76">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="M22" s="95">
+      <c r="M22" s="76">
         <v>42</v>
       </c>
-      <c r="N22" s="99" t="s">
-        <v>107</v>
-      </c>
-      <c r="O22" s="100"/>
-      <c r="P22" s="101">
+      <c r="N22" s="80"/>
+      <c r="O22" s="81"/>
+      <c r="P22" s="82">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q22" s="102" t="s">
-        <v>112</v>
-      </c>
-      <c r="R22" s="103"/>
+      <c r="Q22" s="91" t="s">
+        <v>105</v>
+      </c>
+      <c r="R22" s="83"/>
     </row>
     <row r="23" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
@@ -2504,28 +2562,28 @@
         <v>14</v>
       </c>
       <c r="C23" s="47" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D23" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="E23" s="47" t="s">
-        <v>48</v>
+        <v>37</v>
+      </c>
+      <c r="E23" s="69" t="s">
+        <v>45</v>
       </c>
       <c r="F23" s="48" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G23" s="64" t="s">
-        <v>90</v>
-      </c>
-      <c r="H23" s="70" t="s">
-        <v>67</v>
+        <v>85</v>
+      </c>
+      <c r="H23" s="69" t="s">
+        <v>63</v>
       </c>
       <c r="I23" s="49" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="J23" s="64" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="K23" s="48">
         <v>1</v>
@@ -2538,16 +2596,16 @@
         <v>42</v>
       </c>
       <c r="N23" s="67" t="s">
-        <v>88</v>
-      </c>
-      <c r="O23" s="77">
-        <v>0.32100000000000001</v>
+        <v>83</v>
+      </c>
+      <c r="O23" s="73">
+        <v>0.3337</v>
       </c>
       <c r="P23" s="56">
         <f t="shared" si="2"/>
-        <v>13.482000000000001</v>
-      </c>
-      <c r="Q23" s="49"/>
+        <v>14.0154</v>
+      </c>
+      <c r="Q23" s="69"/>
       <c r="R23" s="50"/>
     </row>
     <row r="24" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -2565,17 +2623,17 @@
       <c r="J24" s="37"/>
       <c r="K24" s="37"/>
       <c r="L24" s="37"/>
-      <c r="M24" s="87" t="s">
-        <v>109</v>
-      </c>
-      <c r="N24" s="88"/>
-      <c r="O24" s="88"/>
-      <c r="P24" s="79">
+      <c r="M24" s="106" t="s">
+        <v>102</v>
+      </c>
+      <c r="N24" s="107"/>
+      <c r="O24" s="107"/>
+      <c r="P24" s="74">
         <f>SUM(P10:P23)</f>
-        <v>29.542300000000004</v>
-      </c>
-      <c r="Q24" s="83"/>
-      <c r="R24" s="84"/>
+        <v>25.4909</v>
+      </c>
+      <c r="Q24" s="102"/>
+      <c r="R24" s="103"/>
     </row>
     <row r="25" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
@@ -2592,17 +2650,17 @@
       <c r="J25" s="10"/>
       <c r="K25" s="10"/>
       <c r="L25" s="10"/>
-      <c r="M25" s="87" t="s">
-        <v>110</v>
-      </c>
-      <c r="N25" s="88"/>
-      <c r="O25" s="88"/>
-      <c r="P25" s="80">
+      <c r="M25" s="106" t="s">
+        <v>103</v>
+      </c>
+      <c r="N25" s="107"/>
+      <c r="O25" s="107"/>
+      <c r="P25" s="75">
         <f>P24/40</f>
-        <v>0.73855750000000009</v>
-      </c>
-      <c r="Q25" s="85"/>
-      <c r="R25" s="86"/>
+        <v>0.63727250000000002</v>
+      </c>
+      <c r="Q25" s="104"/>
+      <c r="R25" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2618,16 +2676,15 @@
     <hyperlink ref="N13" r:id="rId3" xr:uid="{3316A748-B8D9-4599-A88C-2479A2BBEEC0}"/>
     <hyperlink ref="N12" r:id="rId4" xr:uid="{803A24A0-A762-425E-AC20-EA07F09A9367}"/>
     <hyperlink ref="N14" r:id="rId5" xr:uid="{A4B2D320-5CBE-4BB2-B81F-320483F8FBAA}"/>
-    <hyperlink ref="N15" r:id="rId6" xr:uid="{E7C8E6FA-51D5-49E8-8FF8-73BBC39BC3FD}"/>
-    <hyperlink ref="N17" r:id="rId7" xr:uid="{29921090-CC44-4A46-8F19-A30767472E2A}"/>
-    <hyperlink ref="N18" r:id="rId8" xr:uid="{7693C507-9AC2-4CA1-AE08-C5F9CAC53817}"/>
-    <hyperlink ref="N19" r:id="rId9" xr:uid="{BD1D72C5-4EBC-4BD3-8DAE-1C9B36B8D6F8}"/>
-    <hyperlink ref="N20" r:id="rId10" xr:uid="{61BC7777-7602-47EF-ADD6-D12FBA12DD65}"/>
-    <hyperlink ref="N21" r:id="rId11" xr:uid="{F10993F3-EE03-4850-9ADA-3797259DD294}"/>
-    <hyperlink ref="N23" r:id="rId12" xr:uid="{6724C2C5-3322-436E-8518-6AEF36CEAB8B}"/>
+    <hyperlink ref="N17" r:id="rId6" xr:uid="{29921090-CC44-4A46-8F19-A30767472E2A}"/>
+    <hyperlink ref="N18" r:id="rId7" xr:uid="{7693C507-9AC2-4CA1-AE08-C5F9CAC53817}"/>
+    <hyperlink ref="N19" r:id="rId8" xr:uid="{BD1D72C5-4EBC-4BD3-8DAE-1C9B36B8D6F8}"/>
+    <hyperlink ref="N20" r:id="rId9" xr:uid="{61BC7777-7602-47EF-ADD6-D12FBA12DD65}"/>
+    <hyperlink ref="N21" r:id="rId10" xr:uid="{F10993F3-EE03-4850-9ADA-3797259DD294}"/>
+    <hyperlink ref="N23" r:id="rId11" xr:uid="{6724C2C5-3322-436E-8518-6AEF36CEAB8B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId13"/>
-  <drawing r:id="rId14"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId12"/>
+  <drawing r:id="rId13"/>
 </worksheet>
 </file>
--- a/Deliverables/BOM/Electrode-Board/eSpark_BOM_Electrode_Board.xlsx
+++ b/Deliverables/BOM/Electrode-Board/eSpark_BOM_Electrode_Board.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25225"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ManarHarake-sEMGDevice\Deliverables\BOM\Electrode-Board\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\ManarHarake-sEMGDevice\Deliverables\BOM\Electrode-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB5A6380-A497-4E6A-9423-06C3601B9572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="113">
   <si>
     <t>Component list</t>
   </si>
@@ -366,18 +365,21 @@
   </si>
   <si>
     <t>Quantity (1 Board)</t>
+  </si>
+  <si>
+    <t>Quote added from Lulu</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -573,6 +575,14 @@
       <strike/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1165,17 +1175,11 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="18" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="18" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1268,6 +1272,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="16" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1313,7 +1323,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1609,7 +1619,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:R25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1643,15 +1653,15 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="100"/>
-      <c r="K1" s="100"/>
-      <c r="L1" s="100"/>
-      <c r="M1" s="100"/>
-      <c r="N1" s="100"/>
-      <c r="O1" s="100"/>
-      <c r="P1" s="100"/>
-      <c r="Q1" s="100"/>
-      <c r="R1" s="101"/>
+      <c r="J1" s="98"/>
+      <c r="K1" s="98"/>
+      <c r="L1" s="98"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="98"/>
+      <c r="O1" s="98"/>
+      <c r="P1" s="98"/>
+      <c r="Q1" s="98"/>
+      <c r="R1" s="99"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1698,8 +1708,8 @@
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
-      <c r="Q3" s="108"/>
-      <c r="R3" s="109"/>
+      <c r="Q3" s="106"/>
+      <c r="R3" s="107"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1722,8 +1732,8 @@
       <c r="N4" s="6"/>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
-      <c r="Q4" s="110"/>
-      <c r="R4" s="111"/>
+      <c r="Q4" s="108"/>
+      <c r="R4" s="109"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1746,8 +1756,8 @@
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
-      <c r="Q5" s="110"/>
-      <c r="R5" s="111"/>
+      <c r="Q5" s="108"/>
+      <c r="R5" s="109"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1766,8 +1776,8 @@
       <c r="N6" s="6"/>
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
-      <c r="Q6" s="110"/>
-      <c r="R6" s="111"/>
+      <c r="Q6" s="108"/>
+      <c r="R6" s="109"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1786,8 +1796,8 @@
       <c r="N7" s="8"/>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
-      <c r="Q7" s="110"/>
-      <c r="R7" s="111"/>
+      <c r="Q7" s="108"/>
+      <c r="R7" s="109"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1806,8 +1816,8 @@
       <c r="N8" s="8"/>
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
-      <c r="Q8" s="112"/>
-      <c r="R8" s="113"/>
+      <c r="Q8" s="110"/>
+      <c r="R8" s="111"/>
     </row>
     <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2134,53 +2144,53 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="92" t="s">
+      <c r="C15" s="90" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="93" t="s">
+      <c r="D15" s="91" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="92" t="s">
+      <c r="E15" s="90" t="s">
         <v>88</v>
       </c>
-      <c r="F15" s="94" t="s">
+      <c r="F15" s="92" t="s">
         <v>93</v>
       </c>
-      <c r="G15" s="95" t="s">
+      <c r="G15" s="93" t="s">
         <v>93</v>
       </c>
-      <c r="H15" s="95" t="s">
+      <c r="H15" s="93" t="s">
         <v>93</v>
       </c>
-      <c r="I15" s="94" t="s">
+      <c r="I15" s="92" t="s">
         <v>93</v>
       </c>
-      <c r="J15" s="95" t="s">
+      <c r="J15" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="K15" s="93">
+      <c r="K15" s="91">
         <v>1</v>
       </c>
-      <c r="L15" s="92">
+      <c r="L15" s="90">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="M15" s="95" t="s">
+      <c r="M15" s="93" t="s">
         <v>94</v>
       </c>
-      <c r="N15" s="95" t="s">
+      <c r="N15" s="93" t="s">
         <v>93</v>
       </c>
-      <c r="O15" s="96" t="s">
+      <c r="O15" s="94" t="s">
         <v>94</v>
       </c>
-      <c r="P15" s="97" t="s">
+      <c r="P15" s="95" t="s">
         <v>85</v>
       </c>
-      <c r="Q15" s="98" t="s">
+      <c r="Q15" s="96" t="s">
         <v>110</v>
       </c>
-      <c r="R15" s="99" t="s">
+      <c r="R15" s="97" t="s">
         <v>94</v>
       </c>
     </row>
@@ -2190,52 +2200,52 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="84" t="s">
+      <c r="C16" s="82" t="s">
         <v>106</v>
       </c>
-      <c r="D16" s="85" t="s">
+      <c r="D16" s="83" t="s">
         <v>107</v>
       </c>
-      <c r="E16" s="89" t="s">
+      <c r="E16" s="87" t="s">
         <v>88</v>
       </c>
-      <c r="F16" s="84" t="s">
+      <c r="F16" s="82" t="s">
         <v>108</v>
       </c>
-      <c r="G16" s="87" t="s">
+      <c r="G16" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="H16" s="87" t="s">
+      <c r="H16" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="I16" s="86" t="s">
+      <c r="I16" s="84" t="s">
         <v>93</v>
       </c>
-      <c r="J16" s="87" t="s">
+      <c r="J16" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="K16" s="87">
+      <c r="K16" s="85">
         <v>1</v>
       </c>
-      <c r="L16" s="87">
+      <c r="L16" s="85">
         <v>40</v>
       </c>
-      <c r="M16" s="86" t="s">
+      <c r="M16" s="84" t="s">
         <v>93</v>
       </c>
-      <c r="N16" s="87" t="s">
+      <c r="N16" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="O16" s="87" t="s">
+      <c r="O16" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="P16" s="87" t="s">
+      <c r="P16" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="Q16" s="90" t="s">
+      <c r="Q16" s="88" t="s">
         <v>110</v>
       </c>
-      <c r="R16" s="88" t="s">
+      <c r="R16" s="86" t="s">
         <v>92</v>
       </c>
     </row>
@@ -2451,7 +2461,7 @@
       <c r="Q20" s="43"/>
       <c r="R20" s="51"/>
     </row>
-    <row r="21" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="38">
         <f t="shared" si="0"/>
@@ -2544,18 +2554,24 @@
       <c r="M22" s="76">
         <v>42</v>
       </c>
-      <c r="N22" s="80"/>
-      <c r="O22" s="81"/>
-      <c r="P22" s="82">
+      <c r="N22" s="112" t="s">
+        <v>93</v>
+      </c>
+      <c r="O22" s="80">
+        <v>4.7249999999999996</v>
+      </c>
+      <c r="P22" s="81">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="91" t="s">
+        <v>198.45</v>
+      </c>
+      <c r="Q22" s="89" t="s">
         <v>105</v>
       </c>
-      <c r="R22" s="83"/>
+      <c r="R22" s="113" t="s">
+        <v>112</v>
+      </c>
     </row>
-    <row r="23" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="38">
         <f t="shared" si="0"/>
@@ -2623,17 +2639,17 @@
       <c r="J24" s="37"/>
       <c r="K24" s="37"/>
       <c r="L24" s="37"/>
-      <c r="M24" s="106" t="s">
+      <c r="M24" s="104" t="s">
         <v>102</v>
       </c>
-      <c r="N24" s="107"/>
-      <c r="O24" s="107"/>
+      <c r="N24" s="105"/>
+      <c r="O24" s="105"/>
       <c r="P24" s="74">
         <f>SUM(P10:P23)</f>
-        <v>25.4909</v>
-      </c>
-      <c r="Q24" s="102"/>
-      <c r="R24" s="103"/>
+        <v>223.9409</v>
+      </c>
+      <c r="Q24" s="100"/>
+      <c r="R24" s="101"/>
     </row>
     <row r="25" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
@@ -2650,17 +2666,17 @@
       <c r="J25" s="10"/>
       <c r="K25" s="10"/>
       <c r="L25" s="10"/>
-      <c r="M25" s="106" t="s">
+      <c r="M25" s="104" t="s">
         <v>103</v>
       </c>
-      <c r="N25" s="107"/>
-      <c r="O25" s="107"/>
+      <c r="N25" s="105"/>
+      <c r="O25" s="105"/>
       <c r="P25" s="75">
         <f>P24/40</f>
-        <v>0.63727250000000002</v>
-      </c>
-      <c r="Q25" s="104"/>
-      <c r="R25" s="105"/>
+        <v>5.5985224999999996</v>
+      </c>
+      <c r="Q25" s="102"/>
+      <c r="R25" s="103"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2671,17 +2687,17 @@
     <mergeCell ref="Q3:R8"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="N11" r:id="rId1" xr:uid="{A31A8878-273D-426F-AD32-0998730774E5}"/>
-    <hyperlink ref="N10" r:id="rId2" xr:uid="{29DC0929-B5AB-47BC-BFFA-D00E0022C560}"/>
-    <hyperlink ref="N13" r:id="rId3" xr:uid="{3316A748-B8D9-4599-A88C-2479A2BBEEC0}"/>
-    <hyperlink ref="N12" r:id="rId4" xr:uid="{803A24A0-A762-425E-AC20-EA07F09A9367}"/>
-    <hyperlink ref="N14" r:id="rId5" xr:uid="{A4B2D320-5CBE-4BB2-B81F-320483F8FBAA}"/>
-    <hyperlink ref="N17" r:id="rId6" xr:uid="{29921090-CC44-4A46-8F19-A30767472E2A}"/>
-    <hyperlink ref="N18" r:id="rId7" xr:uid="{7693C507-9AC2-4CA1-AE08-C5F9CAC53817}"/>
-    <hyperlink ref="N19" r:id="rId8" xr:uid="{BD1D72C5-4EBC-4BD3-8DAE-1C9B36B8D6F8}"/>
-    <hyperlink ref="N20" r:id="rId9" xr:uid="{61BC7777-7602-47EF-ADD6-D12FBA12DD65}"/>
-    <hyperlink ref="N21" r:id="rId10" xr:uid="{F10993F3-EE03-4850-9ADA-3797259DD294}"/>
-    <hyperlink ref="N23" r:id="rId11" xr:uid="{6724C2C5-3322-436E-8518-6AEF36CEAB8B}"/>
+    <hyperlink ref="N11" r:id="rId1"/>
+    <hyperlink ref="N10" r:id="rId2"/>
+    <hyperlink ref="N13" r:id="rId3"/>
+    <hyperlink ref="N12" r:id="rId4"/>
+    <hyperlink ref="N14" r:id="rId5"/>
+    <hyperlink ref="N17" r:id="rId6"/>
+    <hyperlink ref="N18" r:id="rId7"/>
+    <hyperlink ref="N19" r:id="rId8"/>
+    <hyperlink ref="N20" r:id="rId9"/>
+    <hyperlink ref="N21" r:id="rId10"/>
+    <hyperlink ref="N23" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId12"/>

--- a/Deliverables/BOM/Electrode-Board/eSpark_BOM_Electrode_Board.xlsx
+++ b/Deliverables/BOM/Electrode-Board/eSpark_BOM_Electrode_Board.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25501"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\ManarHarake-sEMGDevice\Deliverables\BOM\Electrode-Board\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\ManarHarake-sEMGDevice\Deliverables\BOM\Electrode-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B471FB35-545E-430B-BA1F-96B4DFB010EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="114">
   <si>
     <t>Component list</t>
   </si>
@@ -368,12 +369,15 @@
   </si>
   <si>
     <t>Quote added from Lulu</t>
+  </si>
+  <si>
+    <t>GRM188R61E106MA73D</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
@@ -626,7 +630,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -908,21 +912,6 @@
         <color indexed="64"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -958,23 +947,23 @@
   </cellStyleXfs>
   <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -984,18 +973,18 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1010,7 +999,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -1020,8 +1009,8 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1033,29 +1022,29 @@
     <xf numFmtId="0" fontId="17" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1148,9 +1137,6 @@
     <xf numFmtId="0" fontId="20" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1160,7 +1146,7 @@
     <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1196,7 +1182,7 @@
     <xf numFmtId="0" fontId="26" fillId="2" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1227,6 +1213,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="4" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="16" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1261,7 +1253,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1273,11 +1265,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="16" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1314,7 +1303,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>1724026</xdr:colOff>
+      <xdr:colOff>1724025</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>180975</xdr:rowOff>
     </xdr:to>
@@ -1323,7 +1312,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1619,31 +1608,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:R25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
+    <col min="2" max="2" width="3.109375" style="26" customWidth="1"/>
     <col min="3" max="3" width="36" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.140625" customWidth="1"/>
-    <col min="5" max="5" width="21.5703125" customWidth="1"/>
-    <col min="6" max="6" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.109375" customWidth="1"/>
+    <col min="5" max="5" width="21.5546875" customWidth="1"/>
+    <col min="6" max="6" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.6640625" customWidth="1"/>
+    <col min="8" max="8" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="7" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="29.42578125" customWidth="1"/>
-    <col min="18" max="18" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="29.44140625" customWidth="1"/>
+    <col min="18" max="18" width="26.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="20"/>
       <c r="C1" s="2"/>
@@ -1653,17 +1642,17 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="98"/>
-      <c r="K1" s="98"/>
-      <c r="L1" s="98"/>
-      <c r="M1" s="98"/>
-      <c r="N1" s="98"/>
-      <c r="O1" s="98"/>
-      <c r="P1" s="98"/>
-      <c r="Q1" s="98"/>
-      <c r="R1" s="99"/>
+      <c r="J1" s="99"/>
+      <c r="K1" s="99"/>
+      <c r="L1" s="99"/>
+      <c r="M1" s="99"/>
+      <c r="N1" s="99"/>
+      <c r="O1" s="99"/>
+      <c r="P1" s="99"/>
+      <c r="Q1" s="99"/>
+      <c r="R1" s="100"/>
     </row>
-    <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="21"/>
       <c r="C2" s="11" t="s">
@@ -1687,7 +1676,7 @@
       <c r="Q2" s="4"/>
       <c r="R2" s="3"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="22"/>
       <c r="C3" s="13" t="s">
@@ -1708,10 +1697,10 @@
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
-      <c r="Q3" s="106"/>
-      <c r="R3" s="107"/>
+      <c r="Q3" s="107"/>
+      <c r="R3" s="108"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="22"/>
       <c r="C4" s="13" t="s">
@@ -1732,10 +1721,10 @@
       <c r="N4" s="6"/>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
-      <c r="Q4" s="108"/>
-      <c r="R4" s="109"/>
+      <c r="Q4" s="109"/>
+      <c r="R4" s="110"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="22"/>
       <c r="C5" s="13" t="s">
@@ -1756,10 +1745,10 @@
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
-      <c r="Q5" s="108"/>
-      <c r="R5" s="109"/>
+      <c r="Q5" s="109"/>
+      <c r="R5" s="110"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="23"/>
       <c r="C6" s="16"/>
@@ -1776,10 +1765,10 @@
       <c r="N6" s="6"/>
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
-      <c r="Q6" s="108"/>
-      <c r="R6" s="109"/>
+      <c r="Q6" s="109"/>
+      <c r="R6" s="110"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="24"/>
       <c r="C7" s="18"/>
@@ -1796,10 +1785,10 @@
       <c r="N7" s="8"/>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
-      <c r="Q7" s="108"/>
-      <c r="R7" s="109"/>
+      <c r="Q7" s="109"/>
+      <c r="R7" s="110"/>
     </row>
-    <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
       <c r="B8" s="27"/>
       <c r="C8" s="28"/>
@@ -1816,10 +1805,10 @@
       <c r="N8" s="8"/>
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
-      <c r="Q8" s="110"/>
-      <c r="R8" s="111"/>
+      <c r="Q8" s="111"/>
+      <c r="R8" s="112"/>
     </row>
-    <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
       <c r="B9" s="30" t="s">
         <v>4</v>
@@ -1873,7 +1862,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="25.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1"/>
       <c r="B10" s="38">
         <f>ROW(B10) - ROW($B$9)</f>
@@ -1888,11 +1877,11 @@
       <c r="E10" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="44" t="s">
+      <c r="F10" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="71" t="s">
-        <v>85</v>
+      <c r="G10" s="113" t="s">
+        <v>113</v>
       </c>
       <c r="H10" s="43" t="s">
         <v>57</v>
@@ -1911,22 +1900,22 @@
         <v>40</v>
       </c>
       <c r="M10" s="43">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N10" s="60" t="s">
         <v>83</v>
       </c>
       <c r="O10" s="61">
-        <v>1.3599999999999999E-2</v>
+        <v>3.2800000000000003E-2</v>
       </c>
       <c r="P10" s="63">
         <f>O10*M10</f>
-        <v>0.81599999999999995</v>
+        <v>1.6400000000000001</v>
       </c>
       <c r="Q10" s="43"/>
       <c r="R10" s="46"/>
     </row>
-    <row r="11" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1"/>
       <c r="B11" s="38">
         <f t="shared" ref="B11:B23" si="0">ROW(B11) - ROW($B$9)</f>
@@ -1944,7 +1933,7 @@
       <c r="F11" s="70" t="s">
         <v>48</v>
       </c>
-      <c r="G11" s="72" t="s">
+      <c r="G11" s="71" t="s">
         <v>81</v>
       </c>
       <c r="H11" s="47" t="s">
@@ -1979,7 +1968,7 @@
       <c r="Q11" s="47"/>
       <c r="R11" s="50"/>
     </row>
-    <row r="12" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
       <c r="B12" s="38">
         <f t="shared" si="0"/>
@@ -2032,7 +2021,7 @@
       <c r="Q12" s="43"/>
       <c r="R12" s="51"/>
     </row>
-    <row r="13" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1"/>
       <c r="B13" s="38">
         <f t="shared" si="0"/>
@@ -2085,7 +2074,7 @@
       <c r="Q13" s="47"/>
       <c r="R13" s="50"/>
     </row>
-    <row r="14" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1"/>
       <c r="B14" s="38">
         <f t="shared" si="0"/>
@@ -2138,118 +2127,118 @@
       <c r="Q14" s="43"/>
       <c r="R14" s="51"/>
     </row>
-    <row r="15" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1"/>
       <c r="B15" s="38">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="90" t="s">
+      <c r="C15" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="91" t="s">
+      <c r="D15" s="90" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="90" t="s">
+      <c r="E15" s="89" t="s">
         <v>88</v>
       </c>
-      <c r="F15" s="92" t="s">
+      <c r="F15" s="91" t="s">
         <v>93</v>
       </c>
-      <c r="G15" s="93" t="s">
+      <c r="G15" s="92" t="s">
         <v>93</v>
       </c>
-      <c r="H15" s="93" t="s">
+      <c r="H15" s="92" t="s">
         <v>93</v>
       </c>
-      <c r="I15" s="92" t="s">
+      <c r="I15" s="91" t="s">
         <v>93</v>
       </c>
-      <c r="J15" s="93" t="s">
+      <c r="J15" s="92" t="s">
         <v>92</v>
       </c>
-      <c r="K15" s="91">
+      <c r="K15" s="90">
         <v>1</v>
       </c>
-      <c r="L15" s="90">
+      <c r="L15" s="89">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="M15" s="93" t="s">
+      <c r="M15" s="92" t="s">
         <v>94</v>
       </c>
-      <c r="N15" s="93" t="s">
+      <c r="N15" s="92" t="s">
         <v>93</v>
       </c>
-      <c r="O15" s="94" t="s">
+      <c r="O15" s="93" t="s">
         <v>94</v>
       </c>
-      <c r="P15" s="95" t="s">
+      <c r="P15" s="94" t="s">
         <v>85</v>
       </c>
-      <c r="Q15" s="96" t="s">
+      <c r="Q15" s="95" t="s">
         <v>110</v>
       </c>
-      <c r="R15" s="97" t="s">
+      <c r="R15" s="96" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
       <c r="B16" s="38">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="82" t="s">
+      <c r="C16" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="D16" s="83" t="s">
+      <c r="D16" s="82" t="s">
         <v>107</v>
       </c>
-      <c r="E16" s="87" t="s">
+      <c r="E16" s="86" t="s">
         <v>88</v>
       </c>
-      <c r="F16" s="82" t="s">
+      <c r="F16" s="81" t="s">
         <v>108</v>
       </c>
-      <c r="G16" s="85" t="s">
+      <c r="G16" s="84" t="s">
         <v>93</v>
       </c>
-      <c r="H16" s="85" t="s">
+      <c r="H16" s="84" t="s">
         <v>93</v>
       </c>
-      <c r="I16" s="84" t="s">
+      <c r="I16" s="83" t="s">
         <v>93</v>
       </c>
-      <c r="J16" s="85" t="s">
+      <c r="J16" s="84" t="s">
         <v>92</v>
       </c>
-      <c r="K16" s="85">
+      <c r="K16" s="84">
         <v>1</v>
       </c>
-      <c r="L16" s="85">
+      <c r="L16" s="84">
         <v>40</v>
       </c>
-      <c r="M16" s="84" t="s">
+      <c r="M16" s="83" t="s">
         <v>93</v>
       </c>
-      <c r="N16" s="85" t="s">
+      <c r="N16" s="84" t="s">
         <v>92</v>
       </c>
-      <c r="O16" s="85" t="s">
+      <c r="O16" s="84" t="s">
         <v>93</v>
       </c>
-      <c r="P16" s="85" t="s">
+      <c r="P16" s="84" t="s">
         <v>93</v>
       </c>
-      <c r="Q16" s="88" t="s">
+      <c r="Q16" s="87" t="s">
         <v>110</v>
       </c>
-      <c r="R16" s="86" t="s">
+      <c r="R16" s="85" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
       <c r="B17" s="38">
         <f t="shared" si="0"/>
@@ -2292,7 +2281,7 @@
       <c r="N17" s="67" t="s">
         <v>83</v>
       </c>
-      <c r="O17" s="73">
+      <c r="O17" s="72">
         <v>8.0000000000000004E-4</v>
       </c>
       <c r="P17" s="56">
@@ -2302,7 +2291,7 @@
       <c r="Q17" s="47"/>
       <c r="R17" s="50"/>
     </row>
-    <row r="18" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
       <c r="B18" s="38">
         <f t="shared" si="0"/>
@@ -2355,7 +2344,7 @@
       <c r="Q18" s="43"/>
       <c r="R18" s="51"/>
     </row>
-    <row r="19" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="38">
         <f t="shared" si="0"/>
@@ -2398,7 +2387,7 @@
       <c r="N19" s="67" t="s">
         <v>83</v>
       </c>
-      <c r="O19" s="73">
+      <c r="O19" s="72">
         <v>6.9999999999999999E-4</v>
       </c>
       <c r="P19" s="56">
@@ -2408,7 +2397,7 @@
       <c r="Q19" s="47"/>
       <c r="R19" s="50"/>
     </row>
-    <row r="20" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1"/>
       <c r="B20" s="38">
         <f t="shared" si="0"/>
@@ -2461,7 +2450,7 @@
       <c r="Q20" s="43"/>
       <c r="R20" s="51"/>
     </row>
-    <row r="21" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
       <c r="B21" s="38">
         <f t="shared" si="0"/>
@@ -2504,7 +2493,7 @@
       <c r="N21" s="67" t="s">
         <v>83</v>
       </c>
-      <c r="O21" s="73">
+      <c r="O21" s="72">
         <v>5.9999999999999995E-4</v>
       </c>
       <c r="P21" s="56">
@@ -2514,64 +2503,64 @@
       <c r="Q21" s="47"/>
       <c r="R21" s="50"/>
     </row>
-    <row r="22" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1"/>
       <c r="B22" s="38">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="76" t="s">
+      <c r="C22" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="D22" s="77" t="s">
+      <c r="D22" s="76" t="s">
         <v>36</v>
       </c>
-      <c r="E22" s="76" t="s">
+      <c r="E22" s="75" t="s">
         <v>44</v>
       </c>
-      <c r="F22" s="77" t="s">
+      <c r="F22" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="G22" s="78" t="s">
+      <c r="G22" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="H22" s="76" t="s">
+      <c r="H22" s="75" t="s">
         <v>62</v>
       </c>
-      <c r="I22" s="79" t="s">
+      <c r="I22" s="78" t="s">
         <v>94</v>
       </c>
-      <c r="J22" s="78" t="s">
+      <c r="J22" s="77" t="s">
         <v>92</v>
       </c>
-      <c r="K22" s="77">
+      <c r="K22" s="76">
         <v>1</v>
       </c>
-      <c r="L22" s="76">
+      <c r="L22" s="75">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="M22" s="76">
+      <c r="M22" s="75">
         <v>42</v>
       </c>
-      <c r="N22" s="112" t="s">
+      <c r="N22" s="97" t="s">
         <v>93</v>
       </c>
-      <c r="O22" s="80">
+      <c r="O22" s="79">
         <v>4.7249999999999996</v>
       </c>
-      <c r="P22" s="81">
+      <c r="P22" s="80">
         <f t="shared" si="2"/>
         <v>198.45</v>
       </c>
-      <c r="Q22" s="89" t="s">
+      <c r="Q22" s="88" t="s">
         <v>105</v>
       </c>
-      <c r="R22" s="113" t="s">
+      <c r="R22" s="98" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
       <c r="B23" s="38">
         <f t="shared" si="0"/>
@@ -2614,7 +2603,7 @@
       <c r="N23" s="67" t="s">
         <v>83</v>
       </c>
-      <c r="O23" s="73">
+      <c r="O23" s="72">
         <v>0.3337</v>
       </c>
       <c r="P23" s="56">
@@ -2624,7 +2613,7 @@
       <c r="Q23" s="69"/>
       <c r="R23" s="50"/>
     </row>
-    <row r="24" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
       <c r="B24" s="33"/>
       <c r="C24" s="34" t="s">
@@ -2639,19 +2628,19 @@
       <c r="J24" s="37"/>
       <c r="K24" s="37"/>
       <c r="L24" s="37"/>
-      <c r="M24" s="104" t="s">
+      <c r="M24" s="105" t="s">
         <v>102</v>
       </c>
-      <c r="N24" s="105"/>
-      <c r="O24" s="105"/>
-      <c r="P24" s="74">
+      <c r="N24" s="106"/>
+      <c r="O24" s="106"/>
+      <c r="P24" s="73">
         <f>SUM(P10:P23)</f>
-        <v>223.9409</v>
-      </c>
-      <c r="Q24" s="100"/>
-      <c r="R24" s="101"/>
+        <v>224.76489999999998</v>
+      </c>
+      <c r="Q24" s="101"/>
+      <c r="R24" s="102"/>
     </row>
-    <row r="25" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
       <c r="B25" s="25"/>
       <c r="C25" s="9" t="s">
@@ -2666,17 +2655,17 @@
       <c r="J25" s="10"/>
       <c r="K25" s="10"/>
       <c r="L25" s="10"/>
-      <c r="M25" s="104" t="s">
+      <c r="M25" s="105" t="s">
         <v>103</v>
       </c>
-      <c r="N25" s="105"/>
-      <c r="O25" s="105"/>
-      <c r="P25" s="75">
+      <c r="N25" s="106"/>
+      <c r="O25" s="106"/>
+      <c r="P25" s="74">
         <f>P24/40</f>
-        <v>5.5985224999999996</v>
-      </c>
-      <c r="Q25" s="102"/>
-      <c r="R25" s="103"/>
+        <v>5.6191224999999996</v>
+      </c>
+      <c r="Q25" s="103"/>
+      <c r="R25" s="104"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2687,17 +2676,17 @@
     <mergeCell ref="Q3:R8"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="N11" r:id="rId1"/>
-    <hyperlink ref="N10" r:id="rId2"/>
-    <hyperlink ref="N13" r:id="rId3"/>
-    <hyperlink ref="N12" r:id="rId4"/>
-    <hyperlink ref="N14" r:id="rId5"/>
-    <hyperlink ref="N17" r:id="rId6"/>
-    <hyperlink ref="N18" r:id="rId7"/>
-    <hyperlink ref="N19" r:id="rId8"/>
-    <hyperlink ref="N20" r:id="rId9"/>
-    <hyperlink ref="N21" r:id="rId10"/>
-    <hyperlink ref="N23" r:id="rId11"/>
+    <hyperlink ref="N11" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="N10" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="N13" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="N12" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="N14" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="N17" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="N18" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="N19" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="N20" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="N21" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="N23" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId12"/>

--- a/Deliverables/BOM/Electrode-Board/eSpark_BOM_Electrode_Board.xlsx
+++ b/Deliverables/BOM/Electrode-Board/eSpark_BOM_Electrode_Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\ManarHarake-sEMGDevice\Deliverables\BOM\Electrode-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B471FB35-545E-430B-BA1F-96B4DFB010EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7B03C32-BFAA-48C9-97C1-F7C58AA87A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -284,9 +284,6 @@
     <t>LCSC</t>
   </si>
   <si>
-    <t>C2922482</t>
-  </si>
-  <si>
     <t>---------</t>
   </si>
   <si>
@@ -372,6 +369,9 @@
   </si>
   <si>
     <t>GRM188R61E106MA73D</t>
+  </si>
+  <si>
+    <t>C91606</t>
   </si>
 </sst>
 </file>
@@ -1221,6 +1221,9 @@
     <xf numFmtId="0" fontId="28" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1264,9 +1267,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1642,15 +1642,15 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="100"/>
+      <c r="J1" s="100"/>
+      <c r="K1" s="100"/>
+      <c r="L1" s="100"/>
+      <c r="M1" s="100"/>
+      <c r="N1" s="100"/>
+      <c r="O1" s="100"/>
+      <c r="P1" s="100"/>
+      <c r="Q1" s="100"/>
+      <c r="R1" s="101"/>
     </row>
     <row r="2" spans="1:18" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
@@ -1697,8 +1697,8 @@
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
-      <c r="Q3" s="107"/>
-      <c r="R3" s="108"/>
+      <c r="Q3" s="108"/>
+      <c r="R3" s="109"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
@@ -1721,8 +1721,8 @@
       <c r="N4" s="6"/>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
-      <c r="Q4" s="109"/>
-      <c r="R4" s="110"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="111"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
@@ -1745,8 +1745,8 @@
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
-      <c r="Q5" s="109"/>
-      <c r="R5" s="110"/>
+      <c r="Q5" s="110"/>
+      <c r="R5" s="111"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
@@ -1765,8 +1765,8 @@
       <c r="N6" s="6"/>
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
-      <c r="Q6" s="109"/>
-      <c r="R6" s="110"/>
+      <c r="Q6" s="110"/>
+      <c r="R6" s="111"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
@@ -1785,8 +1785,8 @@
       <c r="N7" s="8"/>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
-      <c r="Q7" s="109"/>
-      <c r="R7" s="110"/>
+      <c r="Q7" s="110"/>
+      <c r="R7" s="111"/>
     </row>
     <row r="8" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
@@ -1805,8 +1805,8 @@
       <c r="N8" s="8"/>
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
-      <c r="Q8" s="111"/>
-      <c r="R8" s="112"/>
+      <c r="Q8" s="112"/>
+      <c r="R8" s="113"/>
     </row>
     <row r="9" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
@@ -1838,7 +1838,7 @@
         <v>64</v>
       </c>
       <c r="K9" s="31" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L9" s="30" t="s">
         <v>80</v>
@@ -1880,17 +1880,17 @@
       <c r="F10" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="113" t="s">
-        <v>113</v>
+      <c r="G10" s="99" t="s">
+        <v>112</v>
       </c>
       <c r="H10" s="43" t="s">
         <v>57</v>
       </c>
       <c r="I10" s="58" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="J10" s="43" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K10" s="44">
         <v>1</v>
@@ -1984,16 +1984,16 @@
         <v>40</v>
       </c>
       <c r="F12" s="44" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G12" s="59" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H12" s="43" t="s">
         <v>59</v>
       </c>
       <c r="I12" s="45" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J12" s="43" t="s">
         <v>66</v>
@@ -2040,13 +2040,13 @@
         <v>49</v>
       </c>
       <c r="G13" s="64" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H13" s="47" t="s">
         <v>59</v>
       </c>
       <c r="I13" s="52" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J13" s="47" t="s">
         <v>67</v>
@@ -2093,16 +2093,16 @@
         <v>50</v>
       </c>
       <c r="G14" s="59" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H14" s="43" t="s">
+        <v>90</v>
+      </c>
+      <c r="I14" s="45" t="s">
+        <v>103</v>
+      </c>
+      <c r="J14" s="59" t="s">
         <v>91</v>
-      </c>
-      <c r="I14" s="45" t="s">
-        <v>104</v>
-      </c>
-      <c r="J14" s="59" t="s">
-        <v>92</v>
       </c>
       <c r="K14" s="44">
         <v>2</v>
@@ -2140,22 +2140,22 @@
         <v>30</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F15" s="91" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G15" s="92" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H15" s="92" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I15" s="91" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J15" s="92" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K15" s="90">
         <v>1</v>
@@ -2165,22 +2165,22 @@
         <v>40</v>
       </c>
       <c r="M15" s="92" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N15" s="92" t="s">
+        <v>92</v>
+      </c>
+      <c r="O15" s="93" t="s">
         <v>93</v>
       </c>
-      <c r="O15" s="93" t="s">
-        <v>94</v>
-      </c>
       <c r="P15" s="94" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q15" s="95" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="R15" s="96" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2190,28 +2190,28 @@
         <v>7</v>
       </c>
       <c r="C16" s="81" t="s">
+        <v>105</v>
+      </c>
+      <c r="D16" s="82" t="s">
         <v>106</v>
       </c>
-      <c r="D16" s="82" t="s">
+      <c r="E16" s="86" t="s">
+        <v>87</v>
+      </c>
+      <c r="F16" s="81" t="s">
         <v>107</v>
       </c>
-      <c r="E16" s="86" t="s">
-        <v>88</v>
-      </c>
-      <c r="F16" s="81" t="s">
-        <v>108</v>
-      </c>
       <c r="G16" s="84" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H16" s="84" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I16" s="83" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J16" s="84" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K16" s="84">
         <v>1</v>
@@ -2220,22 +2220,22 @@
         <v>40</v>
       </c>
       <c r="M16" s="83" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N16" s="84" t="s">
+        <v>91</v>
+      </c>
+      <c r="O16" s="84" t="s">
         <v>92</v>
       </c>
-      <c r="O16" s="84" t="s">
-        <v>93</v>
-      </c>
       <c r="P16" s="84" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q16" s="87" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="R16" s="85" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -2257,13 +2257,13 @@
         <v>51</v>
       </c>
       <c r="G17" s="64" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H17" s="47" t="s">
         <v>59</v>
       </c>
       <c r="I17" s="49" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J17" s="47" t="s">
         <v>68</v>
@@ -2310,13 +2310,13 @@
         <v>52</v>
       </c>
       <c r="G18" s="59" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H18" s="43" t="s">
         <v>59</v>
       </c>
       <c r="I18" s="45" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J18" s="43" t="s">
         <v>69</v>
@@ -2360,16 +2360,16 @@
         <v>42</v>
       </c>
       <c r="F19" s="48" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G19" s="64" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H19" s="47" t="s">
         <v>60</v>
       </c>
       <c r="I19" s="49" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J19" s="47" t="s">
         <v>70</v>
@@ -2410,22 +2410,22 @@
         <v>34</v>
       </c>
       <c r="E20" s="43" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F20" s="44" t="s">
         <v>43</v>
       </c>
       <c r="G20" s="59" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H20" s="43" t="s">
         <v>61</v>
       </c>
       <c r="I20" s="45" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J20" s="59" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K20" s="44">
         <v>1</v>
@@ -2469,13 +2469,13 @@
         <v>53</v>
       </c>
       <c r="G21" s="64" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H21" s="47" t="s">
         <v>59</v>
       </c>
       <c r="I21" s="49" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J21" s="47" t="s">
         <v>71</v>
@@ -2522,16 +2522,16 @@
         <v>54</v>
       </c>
       <c r="G22" s="77" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H22" s="75" t="s">
         <v>62</v>
       </c>
       <c r="I22" s="78" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J22" s="77" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K22" s="76">
         <v>1</v>
@@ -2544,7 +2544,7 @@
         <v>42</v>
       </c>
       <c r="N22" s="97" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O22" s="79">
         <v>4.7249999999999996</v>
@@ -2554,10 +2554,10 @@
         <v>198.45</v>
       </c>
       <c r="Q22" s="88" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R22" s="98" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2579,16 +2579,16 @@
         <v>55</v>
       </c>
       <c r="G23" s="64" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H23" s="69" t="s">
         <v>63</v>
       </c>
       <c r="I23" s="49" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J23" s="64" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K23" s="48">
         <v>1</v>
@@ -2628,17 +2628,17 @@
       <c r="J24" s="37"/>
       <c r="K24" s="37"/>
       <c r="L24" s="37"/>
-      <c r="M24" s="105" t="s">
-        <v>102</v>
-      </c>
-      <c r="N24" s="106"/>
-      <c r="O24" s="106"/>
+      <c r="M24" s="106" t="s">
+        <v>101</v>
+      </c>
+      <c r="N24" s="107"/>
+      <c r="O24" s="107"/>
       <c r="P24" s="73">
         <f>SUM(P10:P23)</f>
         <v>224.76489999999998</v>
       </c>
-      <c r="Q24" s="101"/>
-      <c r="R24" s="102"/>
+      <c r="Q24" s="102"/>
+      <c r="R24" s="103"/>
     </row>
     <row r="25" spans="1:18" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
@@ -2655,17 +2655,17 @@
       <c r="J25" s="10"/>
       <c r="K25" s="10"/>
       <c r="L25" s="10"/>
-      <c r="M25" s="105" t="s">
-        <v>103</v>
-      </c>
-      <c r="N25" s="106"/>
-      <c r="O25" s="106"/>
+      <c r="M25" s="106" t="s">
+        <v>102</v>
+      </c>
+      <c r="N25" s="107"/>
+      <c r="O25" s="107"/>
       <c r="P25" s="74">
         <f>P24/40</f>
         <v>5.6191224999999996</v>
       </c>
-      <c r="Q25" s="103"/>
-      <c r="R25" s="104"/>
+      <c r="Q25" s="104"/>
+      <c r="R25" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="5">
